--- a/golos_digest/tools/demo.xlsx
+++ b/golos_digest/tools/demo.xlsx
@@ -113,7 +113,7 @@
     <t>Нет экспорта сгенерированных диаграмм в Confluence</t>
   </si>
   <si>
-    <t>Коллеги, добрый день. У вас второй день погибает инференс на GLM, можно что то с этим сделать?</t>
+    <t>Коллеги, добрый день. Работаю в VDI, Windows 10, GigaCode Desktop последней версии, модель по умолчанию GLM-5.3-Flash. Второй день погибает инференс: ответ идёт по 40 секунд, а потом падает с 504. Из-за этого приходится переключаться на другую модель и терять контекст. Можно что-то с этим сделать? Спасибо!</t>
   </si>
   <si>
     <t>+1</t>
@@ -137,7 +137,7 @@
     <t>Нет доступа к Desktop, роль тестировщик.</t>
   </si>
   <si>
-    <t>Индексация монорепы на 2 млн строк идёт больше часа и на 80% падает с out of memory, приходится перезапускать IDE.</t>
+    <t>Добрый день! У меня ноутбук на 16 ГБ, IntelliJ IDEA 2026.2 и плагин GigaCode 3.1, проект — монорепозиторий на 2 млн строк. Индексация идёт больше часа и на 80% падает с out of memory. Приходится перезапускать IDE по несколько раз в день. Заранее благодарю.</t>
   </si>
   <si>
     <t>долго индексирует</t>
